--- a/NBFC-MF/Borrowers/Kamala_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Kamala_Daily.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Loan1" sheetId="4" r:id="rId1"/>
     <sheet name="188" sheetId="6" r:id="rId2"/>
     <sheet name="204" sheetId="7" r:id="rId3"/>
+    <sheet name="224" sheetId="8" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="29">
   <si>
     <t>Date</t>
   </si>
@@ -4917,7 +4918,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>85</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -4954,7 +4955,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>14000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -4991,7 +4992,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>13244.497417797626</v>
+        <v>1.8109176380676217E-9</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -5028,7 +5029,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>26755.502582202374</v>
+        <v>39999.999999998188</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -7178,983 +7179,1053 @@
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A87" s="19"/>
-      <c r="B87" s="24" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A87" s="19">
+        <v>46280</v>
+      </c>
+      <c r="B87" s="24">
+        <f t="shared" si="9"/>
+        <v>86</v>
       </c>
       <c r="C87" s="20"/>
-      <c r="D87" s="21" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E87" s="21" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F87" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G87" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H87" s="21" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D87" s="21">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E87" s="21">
+        <f t="shared" si="7"/>
+        <v>41.245774742365064</v>
+      </c>
+      <c r="F87" s="21">
+        <f t="shared" si="11"/>
+        <v>358.75422525763491</v>
+      </c>
+      <c r="G87" s="21">
+        <f t="shared" si="10"/>
+        <v>12885.743192539991</v>
+      </c>
+      <c r="H87" s="21">
+        <f t="shared" si="8"/>
+        <v>27114.256807460009</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A88" s="2"/>
-      <c r="B88" s="23" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A88" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B88" s="23">
+        <f t="shared" si="9"/>
+        <v>87</v>
       </c>
       <c r="C88" s="3"/>
-      <c r="D88" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E88" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F88" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G88" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H88" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D88" s="4">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E88" s="4">
+        <f t="shared" si="7"/>
+        <v>40.128548811016088</v>
+      </c>
+      <c r="F88" s="4">
+        <f t="shared" si="11"/>
+        <v>359.87145118898388</v>
+      </c>
+      <c r="G88" s="4">
+        <f t="shared" si="10"/>
+        <v>12525.871741351006</v>
+      </c>
+      <c r="H88" s="4">
+        <f t="shared" si="8"/>
+        <v>27474.128258648994</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A89" s="19"/>
-      <c r="B89" s="24" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A89" s="19">
+        <v>46280</v>
+      </c>
+      <c r="B89" s="24">
+        <f t="shared" si="9"/>
+        <v>88</v>
       </c>
       <c r="C89" s="20"/>
-      <c r="D89" s="21" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E89" s="21" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F89" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G89" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H89" s="21" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D89" s="21">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E89" s="21">
+        <f t="shared" si="7"/>
+        <v>39.007843634842089</v>
+      </c>
+      <c r="F89" s="21">
+        <f t="shared" si="11"/>
+        <v>360.99215636515794</v>
+      </c>
+      <c r="G89" s="21">
+        <f t="shared" si="10"/>
+        <v>12164.879584985847</v>
+      </c>
+      <c r="H89" s="21">
+        <f t="shared" si="8"/>
+        <v>27835.120415014153</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A90" s="2"/>
-      <c r="B90" s="23" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A90" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B90" s="23">
+        <f t="shared" si="9"/>
+        <v>89</v>
       </c>
       <c r="C90" s="3"/>
-      <c r="D90" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E90" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F90" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G90" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H90" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D90" s="4">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E90" s="4">
+        <f t="shared" si="7"/>
+        <v>37.88364837884167</v>
+      </c>
+      <c r="F90" s="4">
+        <f t="shared" si="11"/>
+        <v>362.11635162115834</v>
+      </c>
+      <c r="G90" s="4">
+        <f t="shared" si="10"/>
+        <v>11802.763233364689</v>
+      </c>
+      <c r="H90" s="4">
+        <f t="shared" si="8"/>
+        <v>28197.236766635309</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A91" s="19"/>
-      <c r="B91" s="24" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A91" s="19">
+        <v>46280</v>
+      </c>
+      <c r="B91" s="24">
+        <f t="shared" si="9"/>
+        <v>90</v>
       </c>
       <c r="C91" s="20"/>
-      <c r="D91" s="21" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E91" s="21" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F91" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G91" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H91" s="21" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D91" s="21">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E91" s="21">
+        <f t="shared" si="7"/>
+        <v>36.755952174271229</v>
+      </c>
+      <c r="F91" s="21">
+        <f t="shared" si="11"/>
+        <v>363.24404782572879</v>
+      </c>
+      <c r="G91" s="21">
+        <f t="shared" si="10"/>
+        <v>11439.51918553896</v>
+      </c>
+      <c r="H91" s="21">
+        <f t="shared" si="8"/>
+        <v>28560.48081446104</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A92" s="2"/>
-      <c r="B92" s="23" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A92" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B92" s="23">
+        <f t="shared" si="9"/>
+        <v>91</v>
       </c>
       <c r="C92" s="3"/>
-      <c r="D92" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E92" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F92" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G92" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H92" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D92" s="4">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E92" s="4">
+        <f t="shared" si="7"/>
+        <v>35.624744118539944</v>
+      </c>
+      <c r="F92" s="4">
+        <f t="shared" si="11"/>
+        <v>364.37525588146008</v>
+      </c>
+      <c r="G92" s="4">
+        <f t="shared" si="10"/>
+        <v>11075.143929657501</v>
+      </c>
+      <c r="H92" s="4">
+        <f t="shared" si="8"/>
+        <v>28924.856070342499</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A93" s="19"/>
-      <c r="B93" s="24" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A93" s="19">
+        <v>46283</v>
+      </c>
+      <c r="B93" s="24">
+        <f t="shared" si="9"/>
+        <v>92</v>
       </c>
       <c r="C93" s="20"/>
-      <c r="D93" s="21" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E93" s="21" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F93" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G93" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H93" s="21" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D93" s="21">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E93" s="21">
+        <f t="shared" si="7"/>
+        <v>34.490013275104332</v>
+      </c>
+      <c r="F93" s="21">
+        <f t="shared" si="11"/>
+        <v>365.50998672489567</v>
+      </c>
+      <c r="G93" s="21">
+        <f t="shared" si="10"/>
+        <v>10709.633942932605</v>
+      </c>
+      <c r="H93" s="21">
+        <f t="shared" si="8"/>
+        <v>29290.366057067396</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A94" s="2"/>
-      <c r="B94" s="23" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A94" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B94" s="23">
+        <f t="shared" si="9"/>
+        <v>93</v>
       </c>
       <c r="C94" s="3"/>
-      <c r="D94" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E94" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F94" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G94" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H94" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D94" s="4">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E94" s="4">
+        <f t="shared" si="7"/>
+        <v>33.351748673362515</v>
+      </c>
+      <c r="F94" s="4">
+        <f t="shared" si="11"/>
+        <v>366.64825132663748</v>
+      </c>
+      <c r="G94" s="4">
+        <f t="shared" si="10"/>
+        <v>10342.985691605967</v>
+      </c>
+      <c r="H94" s="4">
+        <f t="shared" si="8"/>
+        <v>29657.014308394035</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A95" s="19"/>
-      <c r="B95" s="24" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A95" s="19">
+        <v>46283</v>
+      </c>
+      <c r="B95" s="24">
+        <f t="shared" si="9"/>
+        <v>94</v>
       </c>
       <c r="C95" s="20"/>
-      <c r="D95" s="21" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E95" s="21" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F95" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G95" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H95" s="21" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D95" s="21">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E95" s="21">
+        <f t="shared" si="7"/>
+        <v>32.209939308548186</v>
+      </c>
+      <c r="F95" s="21">
+        <f t="shared" si="11"/>
+        <v>367.7900606914518</v>
+      </c>
+      <c r="G95" s="21">
+        <f t="shared" si="10"/>
+        <v>9975.1956309145153</v>
+      </c>
+      <c r="H95" s="21">
+        <f t="shared" si="8"/>
+        <v>30024.804369085483</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A96" s="2"/>
-      <c r="B96" s="23" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A96" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B96" s="23">
+        <f t="shared" si="9"/>
+        <v>95</v>
       </c>
       <c r="C96" s="3"/>
-      <c r="D96" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E96" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F96" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G96" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H96" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D96" s="4">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E96" s="4">
+        <f t="shared" si="7"/>
+        <v>31.064574141624174</v>
+      </c>
+      <c r="F96" s="4">
+        <f t="shared" si="11"/>
+        <v>368.93542585837582</v>
+      </c>
+      <c r="G96" s="4">
+        <f t="shared" si="10"/>
+        <v>9606.26020505614</v>
+      </c>
+      <c r="H96" s="4">
+        <f t="shared" si="8"/>
+        <v>30393.73979494386</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A97" s="19"/>
-      <c r="B97" s="24" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A97" s="19">
+        <v>46283</v>
+      </c>
+      <c r="B97" s="24">
+        <f t="shared" si="9"/>
+        <v>96</v>
       </c>
       <c r="C97" s="20"/>
-      <c r="D97" s="21" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E97" s="21" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F97" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G97" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H97" s="21" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D97" s="21">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E97" s="21">
+        <f t="shared" si="7"/>
+        <v>29.915642099175752</v>
+      </c>
+      <c r="F97" s="21">
+        <f t="shared" si="11"/>
+        <v>370.08435790082427</v>
+      </c>
+      <c r="G97" s="21">
+        <f t="shared" si="10"/>
+        <v>9236.1758471553148</v>
+      </c>
+      <c r="H97" s="21">
+        <f t="shared" si="8"/>
+        <v>30763.824152844685</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A98" s="2"/>
-      <c r="B98" s="23" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A98" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B98" s="23">
+        <f t="shared" si="9"/>
+        <v>97</v>
       </c>
       <c r="C98" s="3"/>
-      <c r="D98" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E98" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F98" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G98" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H98" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D98" s="4">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E98" s="4">
+        <f t="shared" si="7"/>
+        <v>28.763132073303552</v>
+      </c>
+      <c r="F98" s="4">
+        <f t="shared" si="11"/>
+        <v>371.23686792669645</v>
+      </c>
+      <c r="G98" s="4">
+        <f t="shared" si="10"/>
+        <v>8864.9389792286183</v>
+      </c>
+      <c r="H98" s="4">
+        <f t="shared" si="8"/>
+        <v>31135.061020771383</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A99" s="19"/>
-      <c r="B99" s="24" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A99" s="19">
+        <v>46283</v>
+      </c>
+      <c r="B99" s="24">
+        <f t="shared" si="9"/>
+        <v>98</v>
       </c>
       <c r="C99" s="20"/>
-      <c r="D99" s="21" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E99" s="21" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F99" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G99" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H99" s="21" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D99" s="21">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E99" s="21">
+        <f t="shared" si="7"/>
+        <v>27.607032921516197</v>
+      </c>
+      <c r="F99" s="21">
+        <f t="shared" si="11"/>
+        <v>372.39296707848382</v>
+      </c>
+      <c r="G99" s="21">
+        <f t="shared" si="10"/>
+        <v>8492.5460121501346</v>
+      </c>
+      <c r="H99" s="21">
+        <f t="shared" si="8"/>
+        <v>31507.453987849865</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A100" s="2"/>
-      <c r="B100" s="23" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A100" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B100" s="23">
+        <f t="shared" si="9"/>
+        <v>99</v>
       </c>
       <c r="C100" s="3"/>
-      <c r="D100" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E100" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F100" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G100" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H100" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D100" s="4">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E100" s="4">
+        <f t="shared" si="7"/>
+        <v>26.447333466622556</v>
+      </c>
+      <c r="F100" s="4">
+        <f t="shared" si="11"/>
+        <v>373.55266653337742</v>
+      </c>
+      <c r="G100" s="4">
+        <f t="shared" si="10"/>
+        <v>8118.9933456167573</v>
+      </c>
+      <c r="H100" s="4">
+        <f t="shared" si="8"/>
+        <v>31881.006654383244</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A101" s="19"/>
-      <c r="B101" s="24" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A101" s="19">
+        <v>46283</v>
+      </c>
+      <c r="B101" s="24">
+        <f t="shared" si="9"/>
+        <v>100</v>
       </c>
       <c r="C101" s="20"/>
-      <c r="D101" s="21" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E101" s="21" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F101" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G101" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H101" s="21" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D101" s="21">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E101" s="21">
+        <f t="shared" si="7"/>
+        <v>25.284022496623702</v>
+      </c>
+      <c r="F101" s="21">
+        <f t="shared" si="11"/>
+        <v>374.71597750337628</v>
+      </c>
+      <c r="G101" s="21">
+        <f t="shared" si="10"/>
+        <v>7744.2773681133813</v>
+      </c>
+      <c r="H101" s="21">
+        <f t="shared" si="8"/>
+        <v>32255.72263188662</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A102" s="2"/>
-      <c r="B102" s="23" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A102" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B102" s="23">
+        <f t="shared" si="9"/>
+        <v>101</v>
       </c>
       <c r="C102" s="3"/>
-      <c r="D102" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E102" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F102" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G102" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H102" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D102" s="4">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E102" s="4">
+        <f t="shared" si="7"/>
+        <v>24.117088764604492</v>
+      </c>
+      <c r="F102" s="4">
+        <f t="shared" si="11"/>
+        <v>375.88291123539551</v>
+      </c>
+      <c r="G102" s="4">
+        <f t="shared" si="10"/>
+        <v>7368.3944568779862</v>
+      </c>
+      <c r="H102" s="4">
+        <f t="shared" si="8"/>
+        <v>32631.605543122016</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A103" s="19"/>
-      <c r="B103" s="24" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A103" s="19">
+        <v>46283</v>
+      </c>
+      <c r="B103" s="24">
+        <f t="shared" si="9"/>
+        <v>102</v>
       </c>
       <c r="C103" s="20"/>
-      <c r="D103" s="21" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E103" s="21" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F103" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G103" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H103" s="21" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D103" s="21">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E103" s="21">
+        <f t="shared" si="7"/>
+        <v>22.946520988624847</v>
+      </c>
+      <c r="F103" s="21">
+        <f t="shared" si="11"/>
+        <v>377.05347901137515</v>
+      </c>
+      <c r="G103" s="21">
+        <f t="shared" si="10"/>
+        <v>6991.340977866611</v>
+      </c>
+      <c r="H103" s="21">
+        <f t="shared" si="8"/>
+        <v>33008.65902213339</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A104" s="2"/>
-      <c r="B104" s="23" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A104" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B104" s="23">
+        <f t="shared" si="9"/>
+        <v>103</v>
       </c>
       <c r="C104" s="3"/>
-      <c r="D104" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E104" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F104" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G104" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H104" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D104" s="4">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E104" s="4">
+        <f t="shared" si="7"/>
+        <v>21.772307851610673</v>
+      </c>
+      <c r="F104" s="4">
+        <f t="shared" si="11"/>
+        <v>378.22769214838934</v>
+      </c>
+      <c r="G104" s="4">
+        <f t="shared" si="10"/>
+        <v>6613.113285718222</v>
+      </c>
+      <c r="H104" s="4">
+        <f t="shared" si="8"/>
+        <v>33386.886714281776</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A105" s="19"/>
-      <c r="B105" s="24" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A105" s="19">
+        <v>46283</v>
+      </c>
+      <c r="B105" s="24">
+        <f t="shared" si="9"/>
+        <v>104</v>
       </c>
       <c r="C105" s="20"/>
-      <c r="D105" s="21" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E105" s="21" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F105" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G105" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H105" s="21" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D105" s="21">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E105" s="21">
+        <f t="shared" si="7"/>
+        <v>20.594438001244455</v>
+      </c>
+      <c r="F105" s="21">
+        <f t="shared" si="11"/>
+        <v>379.40556199875556</v>
+      </c>
+      <c r="G105" s="21">
+        <f t="shared" si="10"/>
+        <v>6233.7077237194662</v>
+      </c>
+      <c r="H105" s="21">
+        <f t="shared" si="8"/>
+        <v>33766.292276280532</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A106" s="2"/>
-      <c r="B106" s="23" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A106" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B106" s="23">
+        <f t="shared" si="9"/>
+        <v>105</v>
       </c>
       <c r="C106" s="3"/>
-      <c r="D106" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E106" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F106" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G106" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H106" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D106" s="4">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E106" s="4">
+        <f t="shared" si="7"/>
+        <v>19.412900049855487</v>
+      </c>
+      <c r="F106" s="4">
+        <f t="shared" si="11"/>
+        <v>380.58709995014453</v>
+      </c>
+      <c r="G106" s="4">
+        <f t="shared" si="10"/>
+        <v>5853.1206237693214</v>
+      </c>
+      <c r="H106" s="4">
+        <f t="shared" si="8"/>
+        <v>34146.879376230681</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A107" s="19"/>
-      <c r="B107" s="24" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A107" s="19">
+        <v>46283</v>
+      </c>
+      <c r="B107" s="24">
+        <f t="shared" si="9"/>
+        <v>106</v>
       </c>
       <c r="C107" s="20"/>
-      <c r="D107" s="21" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E107" s="21" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F107" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G107" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H107" s="21" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D107" s="21">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E107" s="21">
+        <f t="shared" si="7"/>
+        <v>18.227682574309785</v>
+      </c>
+      <c r="F107" s="21">
+        <f t="shared" si="11"/>
+        <v>381.77231742569023</v>
+      </c>
+      <c r="G107" s="21">
+        <f t="shared" si="10"/>
+        <v>5471.3483063436315</v>
+      </c>
+      <c r="H107" s="21">
+        <f t="shared" si="8"/>
+        <v>34528.651693656371</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A108" s="2"/>
-      <c r="B108" s="23" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A108" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B108" s="23">
+        <f t="shared" si="9"/>
+        <v>107</v>
       </c>
       <c r="C108" s="3"/>
-      <c r="D108" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E108" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F108" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G108" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H108" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D108" s="4">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E108" s="4">
+        <f t="shared" si="7"/>
+        <v>17.038774115899656</v>
+      </c>
+      <c r="F108" s="4">
+        <f t="shared" si="11"/>
+        <v>382.96122588410037</v>
+      </c>
+      <c r="G108" s="4">
+        <f t="shared" si="10"/>
+        <v>5088.3870804595308</v>
+      </c>
+      <c r="H108" s="4">
+        <f t="shared" si="8"/>
+        <v>34911.612919540472</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A109" s="19"/>
-      <c r="B109" s="24" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A109" s="19">
+        <v>46283</v>
+      </c>
+      <c r="B109" s="24">
+        <f t="shared" si="9"/>
+        <v>108</v>
       </c>
       <c r="C109" s="20"/>
-      <c r="D109" s="21" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E109" s="21" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F109" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G109" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H109" s="21" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D109" s="21">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E109" s="21">
+        <f t="shared" si="7"/>
+        <v>15.846163180232898</v>
+      </c>
+      <c r="F109" s="21">
+        <f t="shared" si="11"/>
+        <v>384.15383681976709</v>
+      </c>
+      <c r="G109" s="21">
+        <f t="shared" si="10"/>
+        <v>4704.2332436397637</v>
+      </c>
+      <c r="H109" s="21">
+        <f t="shared" si="8"/>
+        <v>35295.766756360237</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A110" s="2"/>
-      <c r="B110" s="23" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A110" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B110" s="23">
+        <f t="shared" si="9"/>
+        <v>109</v>
       </c>
       <c r="C110" s="3"/>
-      <c r="D110" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E110" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F110" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G110" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H110" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D110" s="4">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E110" s="4">
+        <f t="shared" si="7"/>
+        <v>14.649838237121683</v>
+      </c>
+      <c r="F110" s="4">
+        <f t="shared" si="11"/>
+        <v>385.35016176287832</v>
+      </c>
+      <c r="G110" s="4">
+        <f t="shared" si="10"/>
+        <v>4318.8830818768856</v>
+      </c>
+      <c r="H110" s="4">
+        <f t="shared" si="8"/>
+        <v>35681.116918123116</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A111" s="19"/>
-      <c r="B111" s="24" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A111" s="19">
+        <v>46283</v>
+      </c>
+      <c r="B111" s="24">
+        <f t="shared" si="9"/>
+        <v>110</v>
       </c>
       <c r="C111" s="20"/>
-      <c r="D111" s="21" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E111" s="21" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F111" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G111" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H111" s="21" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D111" s="21">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E111" s="21">
+        <f t="shared" si="7"/>
+        <v>13.449787720471081</v>
+      </c>
+      <c r="F111" s="21">
+        <f t="shared" si="11"/>
+        <v>386.55021227952892</v>
+      </c>
+      <c r="G111" s="21">
+        <f t="shared" si="10"/>
+        <v>3932.3328695973569</v>
+      </c>
+      <c r="H111" s="21">
+        <f t="shared" si="8"/>
+        <v>36067.667130402646</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A112" s="2"/>
-      <c r="B112" s="23" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A112" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B112" s="23">
+        <f t="shared" si="9"/>
+        <v>111</v>
       </c>
       <c r="C112" s="3"/>
-      <c r="D112" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E112" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F112" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G112" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H112" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D112" s="4">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E112" s="4">
+        <f t="shared" si="7"/>
+        <v>12.246000028167236</v>
+      </c>
+      <c r="F112" s="4">
+        <f t="shared" si="11"/>
+        <v>387.75399997183274</v>
+      </c>
+      <c r="G112" s="4">
+        <f t="shared" si="10"/>
+        <v>3544.578869625524</v>
+      </c>
+      <c r="H112" s="4">
+        <f t="shared" si="8"/>
+        <v>36455.421130374474</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A113" s="19"/>
-      <c r="B113" s="24" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A113" s="19">
+        <v>46283</v>
+      </c>
+      <c r="B113" s="24">
+        <f t="shared" si="9"/>
+        <v>112</v>
       </c>
       <c r="C113" s="20"/>
-      <c r="D113" s="21" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E113" s="21" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F113" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G113" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H113" s="21" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D113" s="21">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E113" s="21">
+        <f t="shared" si="7"/>
+        <v>11.038463521965198</v>
+      </c>
+      <c r="F113" s="21">
+        <f t="shared" si="11"/>
+        <v>388.96153647803482</v>
+      </c>
+      <c r="G113" s="21">
+        <f t="shared" si="10"/>
+        <v>3155.6173331474893</v>
+      </c>
+      <c r="H113" s="21">
+        <f t="shared" si="8"/>
+        <v>36844.382666852514</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A114" s="2"/>
-      <c r="B114" s="23" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A114" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B114" s="23">
+        <f t="shared" si="9"/>
+        <v>113</v>
       </c>
       <c r="C114" s="3"/>
-      <c r="D114" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E114" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F114" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G114" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H114" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D114" s="4">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E114" s="4">
+        <f t="shared" si="7"/>
+        <v>9.8271665273764093</v>
+      </c>
+      <c r="F114" s="4">
+        <f t="shared" si="11"/>
+        <v>390.17283347262361</v>
+      </c>
+      <c r="G114" s="4">
+        <f t="shared" si="10"/>
+        <v>2765.4444996748657</v>
+      </c>
+      <c r="H114" s="4">
+        <f t="shared" si="8"/>
+        <v>37234.555500325136</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A115" s="19"/>
-      <c r="B115" s="24" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A115" s="19">
+        <v>46283</v>
+      </c>
+      <c r="B115" s="24">
+        <f t="shared" si="9"/>
+        <v>114</v>
       </c>
       <c r="C115" s="20"/>
-      <c r="D115" s="21" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E115" s="21" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F115" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G115" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H115" s="21" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D115" s="21">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E115" s="21">
+        <f t="shared" si="7"/>
+        <v>8.6120973335558269</v>
+      </c>
+      <c r="F115" s="21">
+        <f t="shared" si="11"/>
+        <v>391.38790266644418</v>
+      </c>
+      <c r="G115" s="21">
+        <f t="shared" si="10"/>
+        <v>2374.0565970084217</v>
+      </c>
+      <c r="H115" s="21">
+        <f t="shared" si="8"/>
+        <v>37625.943402991579</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A116" s="2"/>
-      <c r="B116" s="23" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A116" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B116" s="23">
+        <f t="shared" si="9"/>
+        <v>115</v>
       </c>
       <c r="C116" s="3"/>
-      <c r="D116" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E116" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F116" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G116" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H116" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D116" s="4">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E116" s="4">
+        <f t="shared" si="7"/>
+        <v>7.393244193188707</v>
+      </c>
+      <c r="F116" s="4">
+        <f t="shared" si="11"/>
+        <v>392.60675580681129</v>
+      </c>
+      <c r="G116" s="4">
+        <f t="shared" si="10"/>
+        <v>1981.4498412016105</v>
+      </c>
+      <c r="H116" s="4">
+        <f t="shared" si="8"/>
+        <v>38018.550158798389</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A117" s="19"/>
-      <c r="B117" s="24" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A117" s="19">
+        <v>46283</v>
+      </c>
+      <c r="B117" s="24">
+        <f t="shared" si="9"/>
+        <v>116</v>
       </c>
       <c r="C117" s="20"/>
-      <c r="D117" s="21" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E117" s="21" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F117" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G117" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H117" s="21" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D117" s="21">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E117" s="21">
+        <f t="shared" si="7"/>
+        <v>6.1705953223770278</v>
+      </c>
+      <c r="F117" s="21">
+        <f t="shared" si="11"/>
+        <v>393.82940467762296</v>
+      </c>
+      <c r="G117" s="21">
+        <f t="shared" si="10"/>
+        <v>1587.6204365239876</v>
+      </c>
+      <c r="H117" s="21">
+        <f t="shared" si="8"/>
+        <v>38412.37956347601</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A118" s="2"/>
-      <c r="B118" s="23" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A118" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B118" s="23">
+        <f t="shared" si="9"/>
+        <v>117</v>
       </c>
       <c r="C118" s="3"/>
-      <c r="D118" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E118" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F118" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G118" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H118" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D118" s="4">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E118" s="4">
+        <f t="shared" si="7"/>
+        <v>4.9441389005255685</v>
+      </c>
+      <c r="F118" s="4">
+        <f t="shared" si="11"/>
+        <v>395.05586109947444</v>
+      </c>
+      <c r="G118" s="4">
+        <f t="shared" si="10"/>
+        <v>1192.5645754245131</v>
+      </c>
+      <c r="H118" s="4">
+        <f t="shared" si="8"/>
+        <v>38807.435424575488</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A119" s="19"/>
-      <c r="B119" s="24" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A119" s="19">
+        <v>46283</v>
+      </c>
+      <c r="B119" s="24">
+        <f t="shared" si="9"/>
+        <v>118</v>
       </c>
       <c r="C119" s="20"/>
-      <c r="D119" s="21" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E119" s="21" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F119" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G119" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H119" s="21" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D119" s="21">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E119" s="21">
+        <f t="shared" si="7"/>
+        <v>3.7138630702276219</v>
+      </c>
+      <c r="F119" s="21">
+        <f t="shared" si="11"/>
+        <v>396.2861369297724</v>
+      </c>
+      <c r="G119" s="21">
+        <f t="shared" si="10"/>
+        <v>796.27843849474073</v>
+      </c>
+      <c r="H119" s="21">
+        <f t="shared" si="8"/>
+        <v>39203.721561505263</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A120" s="2"/>
-      <c r="B120" s="23" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A120" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B120" s="23">
+        <f t="shared" si="9"/>
+        <v>119</v>
       </c>
       <c r="C120" s="3"/>
-      <c r="D120" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E120" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F120" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G120" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H120" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D120" s="4">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E120" s="4">
+        <f t="shared" si="7"/>
+        <v>2.4797559371503599</v>
+      </c>
+      <c r="F120" s="4">
+        <f t="shared" si="11"/>
+        <v>397.52024406284966</v>
+      </c>
+      <c r="G120" s="4">
+        <f t="shared" si="10"/>
+        <v>398.75819443189107</v>
+      </c>
+      <c r="H120" s="4">
+        <f t="shared" si="8"/>
+        <v>39601.241805568112</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A121" s="19"/>
-      <c r="B121" s="24" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="A121" s="19">
+        <v>46283</v>
+      </c>
+      <c r="B121" s="24">
+        <f t="shared" si="9"/>
+        <v>120</v>
       </c>
       <c r="C121" s="20"/>
-      <c r="D121" s="21" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E121" s="21" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F121" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G121" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H121" s="21" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D121" s="21">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E121" s="21">
+        <f t="shared" si="7"/>
+        <v>1.2418055699198371</v>
+      </c>
+      <c r="F121" s="21">
+        <f t="shared" si="11"/>
+        <v>398.75819443008015</v>
+      </c>
+      <c r="G121" s="21">
+        <f t="shared" si="10"/>
+        <v>1.8109176380676217E-9</v>
+      </c>
+      <c r="H121" s="21">
+        <f t="shared" si="8"/>
+        <v>39999.999999998188</v>
       </c>
     </row>
   </sheetData>
@@ -8426,31 +8497,33 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A8" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B8" s="23">
+        <f t="shared" si="3"/>
+        <v>7</v>
       </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E8" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F8" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G8" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H8" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D8" s="4">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E8" s="4">
+        <f t="shared" si="1"/>
+        <v>274.657663164084</v>
+      </c>
+      <c r="F8" s="4">
+        <f t="shared" si="4"/>
+        <v>1125.3423368359161</v>
+      </c>
+      <c r="G8" s="4">
+        <f t="shared" si="5"/>
+        <v>12572.227063286609</v>
+      </c>
+      <c r="H8" s="4">
+        <f t="shared" si="2"/>
+        <v>7427.7729367133907</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>25</v>
@@ -8590,7 +8663,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -8625,7 +8698,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>15400</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -8660,7 +8733,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>13697.569400122526</v>
+        <v>12572.227063286609</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -8695,7 +8768,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>6302.4305998774744</v>
+        <v>7427.7729367133907</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -8793,6 +8866,3519 @@
       </c>
       <c r="H18" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L121"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" style="1" customWidth="1"/>
+    <col min="4" max="7" width="14.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13" style="1" customWidth="1"/>
+    <col min="9" max="9" width="1.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="32.28515625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="33" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="6"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="2"/>
+      <c r="B2" s="23" t="str">
+        <f>IF(A2&lt;&gt;"",1,"")</f>
+        <v/>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="4" t="str">
+        <f t="shared" ref="D2:D65" si="0">IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$9,"")</f>
+        <v/>
+      </c>
+      <c r="E2" s="4" t="str">
+        <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$7*$K$8,"")</f>
+        <v/>
+      </c>
+      <c r="F2" s="4" t="str">
+        <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),D2-E2,"")</f>
+        <v/>
+      </c>
+      <c r="G2" s="4" t="str">
+        <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$7-F2,"")</f>
+        <v/>
+      </c>
+      <c r="H2" s="4" t="str">
+        <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$7-G2,"")</f>
+        <v/>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="26" t="str">
+        <f ca="1">IF(K3&lt;&gt;"",
+   "L" &amp; TEXT(K7,"0") &amp;
+   IF(J10="Weeks","W","D") &amp; K10 &amp;
+   "-" &amp; K3 &amp;
+   "-N" &amp; RIGHT(CELL("filename",A1),LEN(CELL("filename",A1))-FIND("]",CELL("filename",A1))),
+   "")</f>
+        <v>L50000D120-Kamala-N224</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="19"/>
+      <c r="B3" s="24" t="str">
+        <f>IF(A3&lt;&gt;"",B2+1,"")</f>
+        <v/>
+      </c>
+      <c r="C3" s="20"/>
+      <c r="D3" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E3" s="21" t="str">
+        <f t="shared" ref="E3:E66" si="1">IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),G2*$K$8,"")</f>
+        <v/>
+      </c>
+      <c r="F3" s="21" t="str">
+        <f>IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),D3-E3,"")</f>
+        <v/>
+      </c>
+      <c r="G3" s="21" t="str">
+        <f>IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),G2-F3,"")</f>
+        <v/>
+      </c>
+      <c r="H3" s="21" t="str">
+        <f t="shared" ref="H3:H66" si="2">IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),$K$7-G3,"")</f>
+        <v/>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" s="27" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+      <c r="B4" s="23" t="str">
+        <f t="shared" ref="B4:B67" si="3">IF(A4&lt;&gt;"",B3+1,"")</f>
+        <v/>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E4" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F4" s="4" t="str">
+        <f>IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),D4-E4,"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="4" t="str">
+        <f>IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),G3-F4,"")</f>
+        <v/>
+      </c>
+      <c r="H4" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="27"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="19"/>
+      <c r="B5" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C5" s="20"/>
+      <c r="D5" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E5" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F5" s="21" t="str">
+        <f>IF(AND($A5&lt;&gt;"",$B5&lt;&gt;""),D5-E5,"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="21" t="str">
+        <f>IF(AND($A5&lt;&gt;"",$B5&lt;&gt;""),G4-F5,"")</f>
+        <v/>
+      </c>
+      <c r="H5" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="27"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="2"/>
+      <c r="B6" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E6" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F6" s="4" t="str">
+        <f>IF(AND($A6&lt;&gt;"",$B6&lt;&gt;""),D6-E6,"")</f>
+        <v/>
+      </c>
+      <c r="G6" s="4" t="str">
+        <f t="shared" ref="G6:G69" si="4">IF(AND($A6&lt;&gt;"",$B6&lt;&gt;""),G5-F6,"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" s="27"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="19"/>
+      <c r="B7" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C7" s="20"/>
+      <c r="D7" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E7" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F7" s="21" t="str">
+        <f t="shared" ref="F7:F70" si="5">IF(AND($A7&lt;&gt;"",$B7&lt;&gt;""),D7-E7,"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H7" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="28">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="2"/>
+      <c r="B8" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E8" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F8" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G8" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H8" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="29">
+        <f>RATE(K10,-K9,K7)</f>
+        <v>3.1141819460007453E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="19"/>
+      <c r="B9" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C9" s="20"/>
+      <c r="D9" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E9" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F9" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G9" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H9" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="30">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E10" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F10" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G10" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H10" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K10" s="31">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="19"/>
+      <c r="B11" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C11" s="20"/>
+      <c r="D11" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E11" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F11" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G11" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H11" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J11" s="8"/>
+      <c r="L11" s="22"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
+      <c r="B12" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E12" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F12" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G12" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H12" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="10">
+        <f>IFERROR(MAX($B:$B),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="19"/>
+      <c r="B13" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C13" s="20"/>
+      <c r="D13" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E13" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F13" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G13" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H13" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J13" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="12">
+        <f>(K10*K9)-K9*K12</f>
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="2"/>
+      <c r="B14" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E14" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F14" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G14" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H14" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K14" s="12">
+        <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="19"/>
+      <c r="B15" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C15" s="20"/>
+      <c r="D15" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E15" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F15" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G15" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H15" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="K15" s="14">
+        <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="2"/>
+      <c r="B16" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E16" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F16" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G16" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H16" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K16" s="16" t="str">
+        <f>IF(A2,A2, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="19"/>
+      <c r="B17" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C17" s="20"/>
+      <c r="D17" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E17" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F17" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G17" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H17" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J17" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K17" s="18" t="str">
+        <f xml:space="preserve"> IF(A2,(K16 + 120),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E18" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F18" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G18" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H18" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="19"/>
+      <c r="B19" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C19" s="20"/>
+      <c r="D19" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E19" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F19" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G19" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H19" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="2"/>
+      <c r="B20" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E20" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F20" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G20" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H20" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="19"/>
+      <c r="B21" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C21" s="20"/>
+      <c r="D21" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E21" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F21" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G21" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H21" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="2"/>
+      <c r="B22" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E22" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F22" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G22" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H22" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="19"/>
+      <c r="B23" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C23" s="20"/>
+      <c r="D23" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E23" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F23" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G23" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H23" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="2"/>
+      <c r="B24" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E24" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F24" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G24" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H24" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="19"/>
+      <c r="B25" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C25" s="20"/>
+      <c r="D25" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E25" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F25" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G25" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H25" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="2"/>
+      <c r="B26" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C26" s="3"/>
+      <c r="D26" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E26" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F26" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G26" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H26" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="19"/>
+      <c r="B27" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C27" s="20"/>
+      <c r="D27" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E27" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F27" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G27" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H27" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="2"/>
+      <c r="B28" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C28" s="3"/>
+      <c r="D28" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E28" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F28" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G28" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H28" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="19"/>
+      <c r="B29" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C29" s="20"/>
+      <c r="D29" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E29" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F29" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G29" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H29" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="2"/>
+      <c r="B30" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C30" s="3"/>
+      <c r="D30" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E30" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F30" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G30" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H30" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" s="19"/>
+      <c r="B31" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C31" s="20"/>
+      <c r="D31" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E31" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F31" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G31" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H31" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" s="2"/>
+      <c r="B32" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C32" s="3"/>
+      <c r="D32" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E32" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F32" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G32" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H32" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="19"/>
+      <c r="B33" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C33" s="20"/>
+      <c r="D33" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E33" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F33" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G33" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H33" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="2"/>
+      <c r="B34" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C34" s="3"/>
+      <c r="D34" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E34" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F34" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G34" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H34" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="19"/>
+      <c r="B35" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C35" s="20"/>
+      <c r="D35" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E35" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F35" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G35" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H35" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="2"/>
+      <c r="B36" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="D36" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E36" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F36" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G36" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H36" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="19"/>
+      <c r="B37" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C37" s="20"/>
+      <c r="D37" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E37" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F37" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G37" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H37" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="2"/>
+      <c r="B38" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C38" s="3"/>
+      <c r="D38" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E38" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F38" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G38" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H38" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="19"/>
+      <c r="B39" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C39" s="20"/>
+      <c r="D39" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E39" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F39" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G39" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H39" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" s="2"/>
+      <c r="B40" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C40" s="3"/>
+      <c r="D40" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E40" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F40" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G40" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H40" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="19"/>
+      <c r="B41" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C41" s="20"/>
+      <c r="D41" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E41" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F41" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G41" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H41" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="2"/>
+      <c r="B42" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C42" s="3"/>
+      <c r="D42" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E42" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F42" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G42" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H42" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="19"/>
+      <c r="B43" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C43" s="20"/>
+      <c r="D43" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E43" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F43" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G43" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H43" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="2"/>
+      <c r="B44" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C44" s="3"/>
+      <c r="D44" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E44" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F44" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G44" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H44" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="19"/>
+      <c r="B45" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C45" s="20"/>
+      <c r="D45" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E45" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F45" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G45" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H45" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" s="2"/>
+      <c r="B46" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C46" s="3"/>
+      <c r="D46" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E46" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F46" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G46" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H46" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" s="19"/>
+      <c r="B47" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C47" s="20"/>
+      <c r="D47" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E47" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F47" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G47" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H47" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="2"/>
+      <c r="B48" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C48" s="3"/>
+      <c r="D48" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E48" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F48" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G48" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H48" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" s="19"/>
+      <c r="B49" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C49" s="20"/>
+      <c r="D49" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E49" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F49" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G49" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H49" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="2"/>
+      <c r="B50" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C50" s="3"/>
+      <c r="D50" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E50" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F50" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G50" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H50" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" s="19"/>
+      <c r="B51" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C51" s="20"/>
+      <c r="D51" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E51" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F51" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G51" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H51" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52" s="2"/>
+      <c r="B52" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C52" s="3"/>
+      <c r="D52" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E52" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F52" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G52" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H52" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53" s="19"/>
+      <c r="B53" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C53" s="20"/>
+      <c r="D53" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E53" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F53" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G53" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H53" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54" s="2"/>
+      <c r="B54" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C54" s="3"/>
+      <c r="D54" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E54" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F54" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G54" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H54" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55" s="19"/>
+      <c r="B55" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C55" s="20"/>
+      <c r="D55" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E55" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F55" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G55" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H55" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56" s="2"/>
+      <c r="B56" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C56" s="3"/>
+      <c r="D56" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E56" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F56" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G56" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H56" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57" s="19"/>
+      <c r="B57" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C57" s="20"/>
+      <c r="D57" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E57" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F57" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G57" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H57" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A58" s="2"/>
+      <c r="B58" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C58" s="3"/>
+      <c r="D58" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E58" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F58" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G58" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H58" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A59" s="19"/>
+      <c r="B59" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C59" s="20"/>
+      <c r="D59" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E59" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F59" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G59" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H59" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60" s="2"/>
+      <c r="B60" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C60" s="3"/>
+      <c r="D60" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E60" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F60" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G60" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H60" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61" s="19"/>
+      <c r="B61" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C61" s="20"/>
+      <c r="D61" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E61" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F61" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G61" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H61" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62" s="2"/>
+      <c r="B62" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C62" s="3"/>
+      <c r="D62" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E62" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F62" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G62" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H62" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63" s="19"/>
+      <c r="B63" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C63" s="20"/>
+      <c r="D63" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E63" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F63" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G63" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H63" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64" s="2"/>
+      <c r="B64" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C64" s="3"/>
+      <c r="D64" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E64" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F64" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G64" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H64" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65" s="19"/>
+      <c r="B65" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C65" s="20"/>
+      <c r="D65" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E65" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F65" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G65" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H65" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66" s="2"/>
+      <c r="B66" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C66" s="3"/>
+      <c r="D66" s="4" t="str">
+        <f t="shared" ref="D66:D121" si="6">IF(AND($A66&lt;&gt;"",$B66&lt;&gt;""),$K$9,"")</f>
+        <v/>
+      </c>
+      <c r="E66" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F66" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G66" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H66" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67" s="19"/>
+      <c r="B67" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C67" s="20"/>
+      <c r="D67" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E67" s="21" t="str">
+        <f t="shared" ref="E67:E121" si="7">IF(AND($A67&lt;&gt;"",$B67&lt;&gt;""),G66*$K$8,"")</f>
+        <v/>
+      </c>
+      <c r="F67" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G67" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H67" s="21" t="str">
+        <f t="shared" ref="H67:H121" si="8">IF(AND($A67&lt;&gt;"",$B67&lt;&gt;""),$K$7-G67,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68" s="2"/>
+      <c r="B68" s="23" t="str">
+        <f t="shared" ref="B68:B121" si="9">IF(A68&lt;&gt;"",B67+1,"")</f>
+        <v/>
+      </c>
+      <c r="C68" s="3"/>
+      <c r="D68" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E68" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F68" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G68" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H68" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69" s="19"/>
+      <c r="B69" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C69" s="20"/>
+      <c r="D69" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E69" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F69" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G69" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H69" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70" s="2"/>
+      <c r="B70" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C70" s="3"/>
+      <c r="D70" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E70" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F70" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G70" s="4" t="str">
+        <f t="shared" ref="G70:G121" si="10">IF(AND($A70&lt;&gt;"",$B70&lt;&gt;""),G69-F70,"")</f>
+        <v/>
+      </c>
+      <c r="H70" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" s="19"/>
+      <c r="B71" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C71" s="20"/>
+      <c r="D71" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E71" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F71" s="21" t="str">
+        <f t="shared" ref="F71:F121" si="11">IF(AND($A71&lt;&gt;"",$B71&lt;&gt;""),D71-E71,"")</f>
+        <v/>
+      </c>
+      <c r="G71" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H71" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72" s="2"/>
+      <c r="B72" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C72" s="3"/>
+      <c r="D72" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E72" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F72" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G72" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H72" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A73" s="19"/>
+      <c r="B73" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C73" s="20"/>
+      <c r="D73" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E73" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F73" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G73" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H73" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A74" s="2"/>
+      <c r="B74" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C74" s="3"/>
+      <c r="D74" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E74" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F74" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G74" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H74" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75" s="19"/>
+      <c r="B75" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C75" s="20"/>
+      <c r="D75" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E75" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F75" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G75" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H75" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A76" s="2"/>
+      <c r="B76" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C76" s="3"/>
+      <c r="D76" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E76" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F76" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G76" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H76" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A77" s="19"/>
+      <c r="B77" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C77" s="20"/>
+      <c r="D77" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E77" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F77" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G77" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H77" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A78" s="2"/>
+      <c r="B78" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C78" s="3"/>
+      <c r="D78" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E78" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F78" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G78" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H78" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79" s="19"/>
+      <c r="B79" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C79" s="20"/>
+      <c r="D79" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E79" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F79" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G79" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H79" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80" s="2"/>
+      <c r="B80" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C80" s="3"/>
+      <c r="D80" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E80" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F80" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G80" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H80" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A81" s="19"/>
+      <c r="B81" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C81" s="20"/>
+      <c r="D81" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E81" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F81" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G81" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H81" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82" s="2"/>
+      <c r="B82" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C82" s="3"/>
+      <c r="D82" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E82" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F82" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G82" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H82" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A83" s="19"/>
+      <c r="B83" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C83" s="20"/>
+      <c r="D83" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E83" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F83" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G83" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H83" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A84" s="2"/>
+      <c r="B84" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C84" s="3"/>
+      <c r="D84" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E84" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F84" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G84" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H84" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A85" s="19"/>
+      <c r="B85" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C85" s="20"/>
+      <c r="D85" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E85" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F85" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G85" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H85" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A86" s="2"/>
+      <c r="B86" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C86" s="3"/>
+      <c r="D86" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E86" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F86" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G86" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H86" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87" s="19"/>
+      <c r="B87" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C87" s="20"/>
+      <c r="D87" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E87" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F87" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G87" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H87" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A88" s="2"/>
+      <c r="B88" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C88" s="3"/>
+      <c r="D88" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E88" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F88" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G88" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H88" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A89" s="19"/>
+      <c r="B89" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C89" s="20"/>
+      <c r="D89" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E89" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F89" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G89" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H89" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A90" s="2"/>
+      <c r="B90" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C90" s="3"/>
+      <c r="D90" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E90" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F90" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G90" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H90" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A91" s="19"/>
+      <c r="B91" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C91" s="20"/>
+      <c r="D91" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E91" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F91" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G91" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H91" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A92" s="2"/>
+      <c r="B92" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C92" s="3"/>
+      <c r="D92" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E92" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F92" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G92" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H92" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A93" s="19"/>
+      <c r="B93" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C93" s="20"/>
+      <c r="D93" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E93" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F93" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G93" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H93" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A94" s="2"/>
+      <c r="B94" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C94" s="3"/>
+      <c r="D94" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E94" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F94" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G94" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H94" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A95" s="19"/>
+      <c r="B95" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C95" s="20"/>
+      <c r="D95" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E95" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F95" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G95" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H95" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A96" s="2"/>
+      <c r="B96" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C96" s="3"/>
+      <c r="D96" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E96" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F96" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G96" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H96" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A97" s="19"/>
+      <c r="B97" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C97" s="20"/>
+      <c r="D97" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E97" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F97" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G97" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H97" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A98" s="2"/>
+      <c r="B98" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C98" s="3"/>
+      <c r="D98" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E98" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F98" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G98" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H98" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A99" s="19"/>
+      <c r="B99" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C99" s="20"/>
+      <c r="D99" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E99" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F99" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G99" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H99" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A100" s="2"/>
+      <c r="B100" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C100" s="3"/>
+      <c r="D100" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E100" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F100" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G100" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H100" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A101" s="19"/>
+      <c r="B101" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C101" s="20"/>
+      <c r="D101" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E101" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F101" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G101" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H101" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A102" s="2"/>
+      <c r="B102" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C102" s="3"/>
+      <c r="D102" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E102" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F102" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G102" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H102" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A103" s="19"/>
+      <c r="B103" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C103" s="20"/>
+      <c r="D103" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E103" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F103" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G103" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H103" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A104" s="2"/>
+      <c r="B104" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C104" s="3"/>
+      <c r="D104" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E104" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F104" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G104" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H104" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A105" s="19"/>
+      <c r="B105" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C105" s="20"/>
+      <c r="D105" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E105" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F105" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G105" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H105" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A106" s="2"/>
+      <c r="B106" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C106" s="3"/>
+      <c r="D106" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E106" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F106" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G106" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H106" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A107" s="19"/>
+      <c r="B107" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C107" s="20"/>
+      <c r="D107" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E107" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F107" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G107" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H107" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A108" s="2"/>
+      <c r="B108" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C108" s="3"/>
+      <c r="D108" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E108" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F108" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G108" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H108" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A109" s="19"/>
+      <c r="B109" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C109" s="20"/>
+      <c r="D109" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E109" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F109" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G109" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H109" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A110" s="2"/>
+      <c r="B110" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C110" s="3"/>
+      <c r="D110" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E110" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F110" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G110" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H110" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A111" s="19"/>
+      <c r="B111" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C111" s="20"/>
+      <c r="D111" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E111" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F111" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G111" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H111" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A112" s="2"/>
+      <c r="B112" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C112" s="3"/>
+      <c r="D112" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E112" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F112" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G112" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H112" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A113" s="19"/>
+      <c r="B113" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C113" s="20"/>
+      <c r="D113" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E113" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F113" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G113" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H113" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A114" s="2"/>
+      <c r="B114" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C114" s="3"/>
+      <c r="D114" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E114" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F114" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G114" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H114" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A115" s="19"/>
+      <c r="B115" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C115" s="20"/>
+      <c r="D115" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E115" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F115" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G115" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H115" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A116" s="2"/>
+      <c r="B116" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C116" s="3"/>
+      <c r="D116" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E116" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F116" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G116" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H116" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A117" s="19"/>
+      <c r="B117" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C117" s="20"/>
+      <c r="D117" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E117" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F117" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G117" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H117" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A118" s="2"/>
+      <c r="B118" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C118" s="3"/>
+      <c r="D118" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E118" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F118" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G118" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H118" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A119" s="19"/>
+      <c r="B119" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C119" s="20"/>
+      <c r="D119" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E119" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F119" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G119" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H119" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A120" s="2"/>
+      <c r="B120" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C120" s="3"/>
+      <c r="D120" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E120" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F120" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G120" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H120" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A121" s="19"/>
+      <c r="B121" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C121" s="20"/>
+      <c r="D121" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E121" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F121" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G121" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H121" s="21" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>

--- a/NBFC-MF/Borrowers/Kamala_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Kamala_Daily.xlsx
@@ -8534,31 +8534,33 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="19"/>
-      <c r="B9" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A9" s="19">
+        <v>46290</v>
+      </c>
+      <c r="B9" s="24">
+        <f t="shared" si="3"/>
+        <v>8</v>
       </c>
       <c r="C9" s="20"/>
-      <c r="D9" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E9" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F9" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G9" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H9" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D9" s="21">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E9" s="21">
+        <f t="shared" si="1"/>
+        <v>252.09279143638921</v>
+      </c>
+      <c r="F9" s="21">
+        <f t="shared" si="4"/>
+        <v>1147.9072085636108</v>
+      </c>
+      <c r="G9" s="21">
+        <f t="shared" si="5"/>
+        <v>11424.319854722999</v>
+      </c>
+      <c r="H9" s="21">
+        <f t="shared" si="2"/>
+        <v>8575.6801452770014</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>8</v>
@@ -8663,7 +8665,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -8698,7 +8700,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>14000</v>
+        <v>12600</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -8733,7 +8735,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>12572.227063286609</v>
+        <v>11424.319854722999</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -8768,7 +8770,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>7427.7729367133907</v>
+        <v>8575.6801452770014</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -8922,31 +8924,33 @@
       <c r="K1" s="6"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="23" t="str">
+      <c r="A2" s="2">
+        <v>46288</v>
+      </c>
+      <c r="B2" s="23">
         <f>IF(A2&lt;&gt;"",1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="4" t="str">
+      <c r="D2" s="4">
         <f t="shared" ref="D2:D65" si="0">IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$9,"")</f>
-        <v/>
-      </c>
-      <c r="E2" s="4" t="str">
+        <v>500</v>
+      </c>
+      <c r="E2" s="4">
         <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$7*$K$8,"")</f>
-        <v/>
-      </c>
-      <c r="F2" s="4" t="str">
+        <v>155.70909730003726</v>
+      </c>
+      <c r="F2" s="4">
         <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),D2-E2,"")</f>
-        <v/>
-      </c>
-      <c r="G2" s="4" t="str">
+        <v>344.29090269996277</v>
+      </c>
+      <c r="G2" s="4">
         <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$7-F2,"")</f>
-        <v/>
-      </c>
-      <c r="H2" s="4" t="str">
+        <v>49655.709097300038</v>
+      </c>
+      <c r="H2" s="4">
         <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$7-G2,"")</f>
-        <v/>
+        <v>344.29090269996232</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>17</v>
@@ -8962,31 +8966,33 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="19"/>
-      <c r="B3" s="24" t="str">
+      <c r="A3" s="19">
+        <v>46288</v>
+      </c>
+      <c r="B3" s="24">
         <f>IF(A3&lt;&gt;"",B2+1,"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C3" s="20"/>
-      <c r="D3" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E3" s="21" t="str">
+      <c r="D3" s="21">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="E3" s="21">
         <f t="shared" ref="E3:E66" si="1">IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),G2*$K$8,"")</f>
-        <v/>
-      </c>
-      <c r="F3" s="21" t="str">
+        <v>154.63691278667673</v>
+      </c>
+      <c r="F3" s="21">
         <f>IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),D3-E3,"")</f>
-        <v/>
-      </c>
-      <c r="G3" s="21" t="str">
+        <v>345.3630872133233</v>
+      </c>
+      <c r="G3" s="21">
         <f>IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),G2-F3,"")</f>
-        <v/>
-      </c>
-      <c r="H3" s="21" t="str">
+        <v>49310.346010086716</v>
+      </c>
+      <c r="H3" s="21">
         <f t="shared" ref="H3:H66" si="2">IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),$K$7-G3,"")</f>
-        <v/>
+        <v>689.65398991328402</v>
       </c>
       <c r="J3" s="5" t="s">
         <v>10</v>
@@ -8996,31 +9002,33 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="23" t="str">
+      <c r="A4" s="2">
+        <v>46288</v>
+      </c>
+      <c r="B4" s="23">
         <f t="shared" ref="B4:B67" si="3">IF(A4&lt;&gt;"",B3+1,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="C4" s="3"/>
-      <c r="D4" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E4" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F4" s="4" t="str">
+      <c r="D4" s="4">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="E4" s="4">
+        <f t="shared" si="1"/>
+        <v>153.56138929566194</v>
+      </c>
+      <c r="F4" s="4">
         <f>IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),D4-E4,"")</f>
-        <v/>
-      </c>
-      <c r="G4" s="4" t="str">
+        <v>346.43861070433809</v>
+      </c>
+      <c r="G4" s="4">
         <f>IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),G3-F4,"")</f>
-        <v/>
-      </c>
-      <c r="H4" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>48963.907399382377</v>
+      </c>
+      <c r="H4" s="4">
+        <f t="shared" si="2"/>
+        <v>1036.0926006176232</v>
       </c>
       <c r="J4" s="5" t="s">
         <v>11</v>
@@ -9028,31 +9036,33 @@
       <c r="K4" s="27"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="19"/>
-      <c r="B5" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A5" s="19">
+        <v>46288</v>
+      </c>
+      <c r="B5" s="24">
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
       <c r="C5" s="20"/>
-      <c r="D5" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E5" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F5" s="21" t="str">
+      <c r="D5" s="21">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="E5" s="21">
+        <f t="shared" si="1"/>
+        <v>152.48251642880891</v>
+      </c>
+      <c r="F5" s="21">
         <f>IF(AND($A5&lt;&gt;"",$B5&lt;&gt;""),D5-E5,"")</f>
-        <v/>
-      </c>
-      <c r="G5" s="21" t="str">
+        <v>347.51748357119106</v>
+      </c>
+      <c r="G5" s="21">
         <f>IF(AND($A5&lt;&gt;"",$B5&lt;&gt;""),G4-F5,"")</f>
-        <v/>
-      </c>
-      <c r="H5" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>48616.389915811189</v>
+      </c>
+      <c r="H5" s="21">
+        <f t="shared" si="2"/>
+        <v>1383.610084188811</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>12</v>
@@ -9060,31 +9070,33 @@
       <c r="K5" s="27"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A6" s="2">
+        <v>46288</v>
+      </c>
+      <c r="B6" s="23">
+        <f t="shared" si="3"/>
+        <v>5</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E6" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F6" s="4" t="str">
+      <c r="D6" s="4">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="E6" s="4">
+        <f t="shared" si="1"/>
+        <v>151.4002837555519</v>
+      </c>
+      <c r="F6" s="4">
         <f>IF(AND($A6&lt;&gt;"",$B6&lt;&gt;""),D6-E6,"")</f>
-        <v/>
-      </c>
-      <c r="G6" s="4" t="str">
+        <v>348.59971624444813</v>
+      </c>
+      <c r="G6" s="4">
         <f t="shared" ref="G6:G69" si="4">IF(AND($A6&lt;&gt;"",$B6&lt;&gt;""),G5-F6,"")</f>
-        <v/>
-      </c>
-      <c r="H6" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>48267.790199566742</v>
+      </c>
+      <c r="H6" s="4">
+        <f t="shared" si="2"/>
+        <v>1732.2098004332584</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>13</v>
@@ -9290,7 +9302,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -9325,7 +9337,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>60000</v>
+        <v>57500</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -9360,7 +9372,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>60000</v>
+        <v>48267.790199566742</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -9395,7 +9407,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>0</v>
+        <v>1732.2098004332584</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -9428,9 +9440,9 @@
       <c r="J16" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K16" s="16" t="str">
+      <c r="K16" s="16">
         <f>IF(A2,A2, "")</f>
-        <v/>
+        <v>46288</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
@@ -9463,9 +9475,9 @@
       <c r="J17" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="K17" s="18" t="str">
+      <c r="K17" s="18">
         <f xml:space="preserve"> IF(A2,(K16 + 120),"")</f>
-        <v/>
+        <v>46408</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Kamala_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Kamala_Daily.xlsx
@@ -8571,31 +8571,33 @@
       <c r="L9" s="22"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A10" s="2">
+        <v>46297</v>
+      </c>
+      <c r="B10" s="23">
+        <f t="shared" si="3"/>
+        <v>9</v>
       </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E10" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F10" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G10" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H10" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D10" s="4">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E10" s="4">
+        <f t="shared" si="1"/>
+        <v>229.07545878243178</v>
+      </c>
+      <c r="F10" s="4">
+        <f t="shared" si="4"/>
+        <v>1170.9245412175683</v>
+      </c>
+      <c r="G10" s="4">
+        <f t="shared" si="5"/>
+        <v>10253.395313505431</v>
+      </c>
+      <c r="H10" s="4">
+        <f t="shared" si="2"/>
+        <v>9746.6046864945693</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>26</v>
@@ -8605,31 +8607,33 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="19"/>
-      <c r="B11" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A11" s="19">
+        <v>46304</v>
+      </c>
+      <c r="B11" s="24">
+        <f t="shared" si="3"/>
+        <v>10</v>
       </c>
       <c r="C11" s="20"/>
-      <c r="D11" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E11" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F11" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G11" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H11" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D11" s="21">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E11" s="21">
+        <f t="shared" si="1"/>
+        <v>205.59659265386028</v>
+      </c>
+      <c r="F11" s="21">
+        <f t="shared" si="4"/>
+        <v>1194.4034073461398</v>
+      </c>
+      <c r="G11" s="21">
+        <f t="shared" si="5"/>
+        <v>9058.9919061592918</v>
+      </c>
+      <c r="H11" s="21">
+        <f t="shared" si="2"/>
+        <v>10941.008093840708</v>
       </c>
       <c r="J11" s="8"/>
     </row>
@@ -8665,7 +8669,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -8700,7 +8704,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>12600</v>
+        <v>9800</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -8735,7 +8739,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>11424.319854722999</v>
+        <v>9058.9919061592918</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -8770,7 +8774,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>8575.6801452770014</v>
+        <v>10941.008093840708</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -9104,31 +9108,33 @@
       <c r="K6" s="27"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="19"/>
-      <c r="B7" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A7" s="19">
+        <v>46295</v>
+      </c>
+      <c r="B7" s="24">
+        <f t="shared" si="3"/>
+        <v>6</v>
       </c>
       <c r="C7" s="20"/>
-      <c r="D7" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E7" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F7" s="21" t="str">
+      <c r="D7" s="21">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="E7" s="21">
+        <f t="shared" si="1"/>
+        <v>150.31468081284245</v>
+      </c>
+      <c r="F7" s="21">
         <f t="shared" ref="F7:F70" si="5">IF(AND($A7&lt;&gt;"",$B7&lt;&gt;""),D7-E7,"")</f>
-        <v/>
-      </c>
-      <c r="G7" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H7" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>349.68531918715757</v>
+      </c>
+      <c r="G7" s="21">
+        <f t="shared" si="4"/>
+        <v>47918.104880379586</v>
+      </c>
+      <c r="H7" s="21">
+        <f t="shared" si="2"/>
+        <v>2081.8951196204143</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>7</v>
@@ -9138,31 +9144,33 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A8" s="2">
+        <v>46295</v>
+      </c>
+      <c r="B8" s="23">
+        <f t="shared" si="3"/>
+        <v>7</v>
       </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E8" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F8" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G8" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H8" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D8" s="4">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="E8" s="4">
+        <f t="shared" si="1"/>
+        <v>149.22569710504831</v>
+      </c>
+      <c r="F8" s="4">
+        <f t="shared" si="5"/>
+        <v>350.77430289495169</v>
+      </c>
+      <c r="G8" s="4">
+        <f t="shared" si="4"/>
+        <v>47567.330577484638</v>
+      </c>
+      <c r="H8" s="4">
+        <f t="shared" si="2"/>
+        <v>2432.6694225153624</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>14</v>
@@ -9173,31 +9181,33 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="19"/>
-      <c r="B9" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A9" s="19">
+        <v>46295</v>
+      </c>
+      <c r="B9" s="24">
+        <f t="shared" si="3"/>
+        <v>8</v>
       </c>
       <c r="C9" s="20"/>
-      <c r="D9" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E9" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F9" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G9" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H9" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D9" s="21">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="E9" s="21">
+        <f t="shared" si="1"/>
+        <v>148.13332210385187</v>
+      </c>
+      <c r="F9" s="21">
+        <f t="shared" si="5"/>
+        <v>351.86667789614813</v>
+      </c>
+      <c r="G9" s="21">
+        <f t="shared" si="4"/>
+        <v>47215.463899588489</v>
+      </c>
+      <c r="H9" s="21">
+        <f t="shared" si="2"/>
+        <v>2784.5361004115111</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>8</v>
@@ -9207,31 +9217,33 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A10" s="2">
+        <v>46295</v>
+      </c>
+      <c r="B10" s="23">
+        <f t="shared" si="3"/>
+        <v>9</v>
       </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E10" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F10" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G10" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H10" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D10" s="4">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="E10" s="4">
+        <f t="shared" si="1"/>
+        <v>147.03754524814843</v>
+      </c>
+      <c r="F10" s="4">
+        <f t="shared" si="5"/>
+        <v>352.96245475185157</v>
+      </c>
+      <c r="G10" s="4">
+        <f t="shared" si="4"/>
+        <v>46862.501444836635</v>
+      </c>
+      <c r="H10" s="4">
+        <f t="shared" si="2"/>
+        <v>3137.4985551633654</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>15</v>
@@ -9241,201 +9253,213 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="19"/>
-      <c r="B11" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A11" s="19">
+        <v>46295</v>
+      </c>
+      <c r="B11" s="24">
+        <f t="shared" si="3"/>
+        <v>10</v>
       </c>
       <c r="C11" s="20"/>
-      <c r="D11" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E11" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F11" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G11" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H11" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D11" s="21">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="E11" s="21">
+        <f t="shared" si="1"/>
+        <v>145.93835594394409</v>
+      </c>
+      <c r="F11" s="21">
+        <f t="shared" si="5"/>
+        <v>354.06164405605591</v>
+      </c>
+      <c r="G11" s="21">
+        <f t="shared" si="4"/>
+        <v>46508.439800780579</v>
+      </c>
+      <c r="H11" s="21">
+        <f t="shared" si="2"/>
+        <v>3491.5601992194206</v>
       </c>
       <c r="J11" s="8"/>
       <c r="L11" s="22"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A12" s="2">
+        <v>46295</v>
+      </c>
+      <c r="B12" s="23">
+        <f t="shared" si="3"/>
+        <v>11</v>
       </c>
       <c r="C12" s="3"/>
-      <c r="D12" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E12" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F12" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G12" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H12" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D12" s="4">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="E12" s="4">
+        <f t="shared" si="1"/>
+        <v>144.83574356425339</v>
+      </c>
+      <c r="F12" s="4">
+        <f t="shared" si="5"/>
+        <v>355.16425643574661</v>
+      </c>
+      <c r="G12" s="4">
+        <f t="shared" si="4"/>
+        <v>46153.275544344833</v>
+      </c>
+      <c r="H12" s="4">
+        <f t="shared" si="2"/>
+        <v>3846.7244556551668</v>
       </c>
       <c r="J12" s="9" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="19"/>
-      <c r="B13" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A13" s="19">
+        <v>46300</v>
+      </c>
+      <c r="B13" s="24">
+        <f t="shared" si="3"/>
+        <v>12</v>
       </c>
       <c r="C13" s="20"/>
-      <c r="D13" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E13" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F13" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G13" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H13" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D13" s="21">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="E13" s="21">
+        <f t="shared" si="1"/>
+        <v>143.7296974489964</v>
+      </c>
+      <c r="F13" s="21">
+        <f t="shared" si="5"/>
+        <v>356.27030255100362</v>
+      </c>
+      <c r="G13" s="21">
+        <f t="shared" si="4"/>
+        <v>45797.005241793828</v>
+      </c>
+      <c r="H13" s="21">
+        <f t="shared" si="2"/>
+        <v>4202.9947582061723</v>
       </c>
       <c r="J13" s="25" t="s">
         <v>22</v>
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>57500</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A14" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B14" s="23">
+        <f t="shared" si="3"/>
+        <v>13</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E14" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F14" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G14" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H14" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D14" s="4">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="E14" s="4">
+        <f t="shared" si="1"/>
+        <v>142.62020690489584</v>
+      </c>
+      <c r="F14" s="4">
+        <f t="shared" si="5"/>
+        <v>357.37979309510416</v>
+      </c>
+      <c r="G14" s="4">
+        <f t="shared" si="4"/>
+        <v>45439.625448698724</v>
+      </c>
+      <c r="H14" s="4">
+        <f t="shared" si="2"/>
+        <v>4560.3745513012764</v>
       </c>
       <c r="J14" s="11" t="s">
         <v>23</v>
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>48267.790199566742</v>
+        <v>42540.228557637194</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="19"/>
-      <c r="B15" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A15" s="19">
+        <v>46300</v>
+      </c>
+      <c r="B15" s="24">
+        <f t="shared" si="3"/>
+        <v>14</v>
       </c>
       <c r="C15" s="20"/>
-      <c r="D15" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E15" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F15" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G15" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H15" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D15" s="21">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="E15" s="21">
+        <f t="shared" si="1"/>
+        <v>141.5072612053736</v>
+      </c>
+      <c r="F15" s="21">
+        <f t="shared" si="5"/>
+        <v>358.4927387946264</v>
+      </c>
+      <c r="G15" s="21">
+        <f t="shared" si="4"/>
+        <v>45081.132709904094</v>
+      </c>
+      <c r="H15" s="21">
+        <f t="shared" si="2"/>
+        <v>4918.8672900959064</v>
       </c>
       <c r="J15" s="13" t="s">
         <v>6</v>
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>1732.2098004332584</v>
+        <v>7459.7714423628058</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A16" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B16" s="23">
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="C16" s="3"/>
-      <c r="D16" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E16" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F16" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G16" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H16" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D16" s="4">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="E16" s="4">
+        <f t="shared" si="1"/>
+        <v>140.39084959044698</v>
+      </c>
+      <c r="F16" s="4">
+        <f t="shared" si="5"/>
+        <v>359.60915040955302</v>
+      </c>
+      <c r="G16" s="4">
+        <f t="shared" si="4"/>
+        <v>44721.523559494541</v>
+      </c>
+      <c r="H16" s="4">
+        <f t="shared" si="2"/>
+        <v>5278.4764405054593</v>
       </c>
       <c r="J16" s="15" t="s">
         <v>18</v>
@@ -9446,31 +9470,33 @@
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="19"/>
-      <c r="B17" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A17" s="19">
+        <v>46300</v>
+      </c>
+      <c r="B17" s="24">
+        <f t="shared" si="3"/>
+        <v>16</v>
       </c>
       <c r="C17" s="20"/>
-      <c r="D17" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E17" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F17" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G17" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H17" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D17" s="21">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="E17" s="21">
+        <f t="shared" si="1"/>
+        <v>139.27096126662488</v>
+      </c>
+      <c r="F17" s="21">
+        <f t="shared" si="5"/>
+        <v>360.72903873337509</v>
+      </c>
+      <c r="G17" s="21">
+        <f t="shared" si="4"/>
+        <v>44360.794520761163</v>
+      </c>
+      <c r="H17" s="21">
+        <f t="shared" si="2"/>
+        <v>5639.2054792388371</v>
       </c>
       <c r="J17" s="17" t="s">
         <v>19</v>
@@ -9481,145 +9507,155 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A18" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B18" s="23">
+        <f t="shared" si="3"/>
+        <v>17</v>
       </c>
       <c r="C18" s="3"/>
-      <c r="D18" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E18" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F18" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G18" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H18" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D18" s="4">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="E18" s="4">
+        <f t="shared" si="1"/>
+        <v>138.14758540680319</v>
+      </c>
+      <c r="F18" s="4">
+        <f t="shared" si="5"/>
+        <v>361.85241459319684</v>
+      </c>
+      <c r="G18" s="4">
+        <f t="shared" si="4"/>
+        <v>43998.942106167968</v>
+      </c>
+      <c r="H18" s="4">
+        <f t="shared" si="2"/>
+        <v>6001.0578938320323</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="19"/>
-      <c r="B19" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A19" s="19">
+        <v>46305</v>
+      </c>
+      <c r="B19" s="24">
+        <f t="shared" si="3"/>
+        <v>18</v>
       </c>
       <c r="C19" s="20"/>
-      <c r="D19" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E19" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F19" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G19" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H19" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D19" s="21">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="E19" s="21">
+        <f t="shared" si="1"/>
+        <v>137.02071115016028</v>
+      </c>
+      <c r="F19" s="21">
+        <f t="shared" si="5"/>
+        <v>362.97928884983969</v>
+      </c>
+      <c r="G19" s="21">
+        <f t="shared" si="4"/>
+        <v>43635.962817318126</v>
+      </c>
+      <c r="H19" s="21">
+        <f t="shared" si="2"/>
+        <v>6364.0371826818737</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A20" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B20" s="23">
+        <f t="shared" si="3"/>
+        <v>19</v>
       </c>
       <c r="C20" s="3"/>
-      <c r="D20" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E20" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F20" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G20" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H20" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D20" s="4">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="E20" s="4">
+        <f t="shared" si="1"/>
+        <v>135.89032760205194</v>
+      </c>
+      <c r="F20" s="4">
+        <f t="shared" si="5"/>
+        <v>364.10967239794809</v>
+      </c>
+      <c r="G20" s="4">
+        <f t="shared" si="4"/>
+        <v>43271.853144920176</v>
+      </c>
+      <c r="H20" s="4">
+        <f t="shared" si="2"/>
+        <v>6728.1468550798236</v>
       </c>
       <c r="J20" s="22"/>
       <c r="K20" s="22"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="19"/>
-      <c r="B21" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A21" s="19">
+        <v>46305</v>
+      </c>
+      <c r="B21" s="24">
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="C21" s="20"/>
-      <c r="D21" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E21" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F21" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G21" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H21" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D21" s="21">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="E21" s="21">
+        <f t="shared" si="1"/>
+        <v>134.75642383390598</v>
+      </c>
+      <c r="F21" s="21">
+        <f t="shared" si="5"/>
+        <v>365.24357616609404</v>
+      </c>
+      <c r="G21" s="21">
+        <f t="shared" si="4"/>
+        <v>42906.60956875408</v>
+      </c>
+      <c r="H21" s="21">
+        <f t="shared" si="2"/>
+        <v>7093.3904312459199</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A22" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B22" s="23">
+        <f t="shared" si="3"/>
+        <v>21</v>
       </c>
       <c r="C22" s="3"/>
-      <c r="D22" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E22" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F22" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G22" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H22" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D22" s="4">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="E22" s="4">
+        <f t="shared" si="1"/>
+        <v>133.61898888311677</v>
+      </c>
+      <c r="F22" s="4">
+        <f t="shared" si="5"/>
+        <v>366.3810111168832</v>
+      </c>
+      <c r="G22" s="4">
+        <f t="shared" si="4"/>
+        <v>42540.228557637194</v>
+      </c>
+      <c r="H22" s="4">
+        <f t="shared" si="2"/>
+        <v>7459.7714423628058</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
